--- a/doc/指令配置总表.xlsx
+++ b/doc/指令配置总表.xlsx
@@ -601,7 +601,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1474,7 +1474,59 @@
         <v>45</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>第一卷</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>60015</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6001501</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>野外打野</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>持续性</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>状态 == IDLE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>气血:-2</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1天/Tick</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>掉落池:Drop_60015, 随机修为</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>切至 EXPLORING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>